--- a/Data Nvidia.xlsx
+++ b/Data Nvidia.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B80333F4-D9AE-475C-8CD0-B4B0859504FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9312" yWindow="984" windowWidth="13356" windowHeight="8880" xr2:uid="{5F685CF0-D425-43C0-AA89-DF601D3B4FB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F685CF0-D425-43C0-AA89-DF601D3B4FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
